--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_004/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_004/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -720,52 +725,12 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1126,11 +1091,6 @@
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1408,17 +1368,17 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Fan Module CFD Credibility Assessment</t>
+          <t>Fan Module CFD Credibility Check</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Steady RANS CFD model to predict pressure rise and shaft power for an in-duct axial fan used in electronics cooling</t>
+          <t>Steady RANS prediction of pressure rise and shaft power for in-duct axial fan electronics cooling</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024R1 steady RANS (k-ω SST with MRF) model predicts fan pressure rise (Δp) and shaft power (torque) over 0.12–0.24 kg/s mass flow and 2400–3600 rpm, ambient air at 25°C. Used for fan selection and operating point decisions in an electronics cooling design context. Success criteria: within 5% on Δp and within 7% on power. No safety-critical certification claim; design guidance grade only.</t>
+          <t>ANSYS Fluent 2024R1 steady RANS (k-ω SST, MRF) model used to predict fan pressure rise (Δp) and shaft power (torque) over 0.12–0.24 kg/s mass flow and 2400–3600 rpm, at 25°C ambient air. Used for fan selection and operating point decisions in an electronics cooling application. Success criteria: within 5% on Δp and within 7% on power across the operating envelope.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1448,7 +1408,7 @@
       </c>
       <c r="I3" s="39" t="inlineStr">
         <is>
-          <t>P. Nguyen</t>
+          <t>P. Nguyen, V&amp;V Coordinator</t>
         </is>
       </c>
       <c r="J3" s="22" t="inlineStr">
@@ -1456,9 +1416,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2054,7 +2014,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Fan Pressure Rise and Power Accuracy Requirement</t>
+          <t>Fan Performance Accuracy Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2064,7 +2024,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model predictions of Δp and shaft power must fall within 5% and 7% respectively of measured values across the stated operating envelope (0.12–0.24 kg/s, 2400–3600 rpm) as agreed with the thermal team up front.</t>
+          <t>Model must predict fan Δp within 5% and shaft power within 7% across the stated operating envelope (0.12–0.24 kg/s, 2400–3600 rpm) relative to ISO 5801 bench test data, for design-guidance-grade fan selection decisions.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2086,13 +2046,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024R1 Steady RANS MRF Model</t>
+          <t>Steady RANS Fan CFD Model</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Steady incompressible RANS model using k-ω SST turbulence closure with curvature correction and Moving Reference Frame rotor treatment; second-order upwind convection, pressure–velocity coupled scheme with pseudo-transient ramp; double precision; run on RHEL 8.8 dual EPYC 7543.</t>
+          <t>ANSYS Fluent 2024R1, double-precision, k-ω SST with curvature correction, MRF rotor treatment, incompressible isothermal flow; geometry from production CAD with tip clearance at 0.38 mm.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2106,13 +2066,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>ISO 5801 Bench Test Data — E-14 Rig, Gantt Lab</t>
+          <t>ISO 5801 Bench Test Dataset (E-14 Rig, Gantt Lab)</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Experimental pressure rise and power measurements across nine operating points on the production fan, collected per ISO 5801 with calibrated static taps (±0.25% FS), orifice plate mass flow meter, and optical tachometer (±0.2%); data uncertainty 1.5% Δp, 1.2% power; hold-out point at 3200 rpm / 0.18 kg/s reserved.</t>
+          <t>Experimental pressure rise and shaft power measurements across nine operating points on the E-14 rig, acquired per ISO 5801 with calibrated static taps (±0.25% FS), orifice plate, and optical tach (±0.2%); one hold-out point reserved at 3200 rpm / 0.18 kg/s.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2126,13 +2086,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Canonical Toolchain Verification Cases</t>
+          <t>Canonical Benchmark and Cross-Code Dataset</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Laminar pipe flow, backward-facing step, and rotating cavity benchmark cases used to sanity-check the ANSYS Fluent solver setup; cross-check with OpenFOAM v10 at one operating point (Δp difference 1.8%).</t>
+          <t>Laminar pipe flow, backward-facing step, and rotating cavity results used for toolchain sanity checks; plus OpenFOAM v10 cross-run at one operating point (Δp difference 1.8%).</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2282,7 +2242,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study (Grid Convergence Index)</t>
+          <t>Mesh Convergence / Discretization Study</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2297,12 +2257,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Three structured grids (6.1M, 12.4M, 24.8M cells) were run; y+ ≈ 1 on fine grid. Monotonic convergence observed; Richardson extrapolation performed.</t>
+          <t>Three structured grids (6.1M, 12.4M, 24.8M cells) run at consistent solver settings; monotonic convergence confirmed. Richardson/GCI-style extrapolation performed.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Extrapolated (grid-independent) Δp and power values</t>
+          <t>Extrapolated (grid-independent) solution</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2312,7 +2272,7 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI-style analysis</t>
+          <t>Richardson extrapolation / Grid Convergence Index</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
@@ -2329,7 +2289,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Pressure Rise Comparison — Nine Operating Points vs ISO 5801 Data</t>
+          <t>ISO 5801 Operating-Point Validation (Nine Points)</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2340,12 +2300,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Steady RANS Δp predictions compared to ISO 5801 bench measurements across nine operating points; hold-out point (3200 rpm, 0.18 kg/s) included as blind test.</t>
+          <t>CFD predictions of Δp and shaft power compared to ISO 5801 bench measurements across nine operating points, including a blind hold-out at 3200 rpm / 0.18 kg/s. RMS and worst-case errors computed. No post-hoc tuning applied.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>ISO 5801 experimental measurements, E-14 rig, Gantt Lab</t>
+          <t>ISO 5801 bench test data (E-14 rig, Gantt Lab)</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2355,12 +2315,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>Combined uncertainty (root-sum-square of grid, iteration, model-form, and input uncertainties); test uncertainty 1.5% Δp</t>
+          <t>Root-sum-square combination of grid uncertainty (1.3%), model-form spread (2.0%), and input uncertainty (2.1%); test data uncertainty 1.5% Δp / 1.2% power</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>RMS error 3.2% on Δp (acceptance threshold 5%)</t>
+          <t>RMS 3.2% Δp, 4.6% power; worst case 5.6% power (low-flow end); combined model uncertainty ~3.2% on Δp</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2372,7 +2332,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Shaft Power Comparison — Nine Operating Points vs ISO 5801 Data</t>
+          <t>Turbulence Model Sensitivity / Model-Form Check</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2383,12 +2343,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Steady RANS torque/power predictions compared to ISO 5801 measurements; worst case near low-flow end where inlet swirl is more pronounced.</t>
+          <t>Two operating points re-run with Spalart–Allmaras turbulence model to assess model-form uncertainty relative to baseline k-ω SST with curvature correction.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>ISO 5801 experimental measurements, E-14 rig, Gantt Lab</t>
+          <t>k-ω SST baseline predictions</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2398,12 +2358,12 @@
       </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>Combined uncertainty propagation; test uncertainty 1.2% power</t>
+          <t>Model-form spread (SST vs SA)</t>
         </is>
       </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>RMS error 4.6% on power; worst-case 5.6% (acceptance threshold 7%)</t>
+          <t>Bias ≤2.5% in Δp between turbulence models</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2415,7 +2375,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Turbulence Model Form Uncertainty — SST vs Spalart–Allmaras Spot Checks</t>
+          <t>Canonical Toolchain Verification and Cross-Code Check</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2426,27 +2386,23 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Two spot-check operating points run with Spalart–Allmaras in addition to k-ω SST; bias in Δp recorded as model-form spread and propagated into combined uncertainty.</t>
+          <t>ANSYS Fluent toolchain verified on laminar pipe flow, backward-facing step, and rotating cavity benchmarks. One operating point cross-run with OpenFOAM v10 to check solver implementation consistency.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>k-ω SST baseline predictions</t>
+          <t>Published reference solutions for benchmark cases; OpenFOAM v10 for cross-code</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>Deterministic model-form spread (inter-model bias)</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>SST vs SA bias ≤2.5% in Δp; model-form contribution to combined UQ ~2.0%</t>
+          <t>Benchmark results within published tolerances; OpenFOAM Δp difference 1.8%</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2456,43 +2412,14 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>Solver Cross-Code Verification — OpenFOAM v10 Comparison</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="24" t="n"/>
       <c r="C7" s="33" t="n"/>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>One operating point re-run in OpenFOAM v10 to cross-verify the Fluent implementation; Δp difference recorded.</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="inlineStr">
-        <is>
-          <t>ANSYS Fluent 2024R1 prediction at same operating point</t>
-        </is>
-      </c>
-      <c r="F7" s="41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="33" t="n"/>
       <c r="G7" s="33" t="n"/>
-      <c r="H7" s="41" t="inlineStr">
-        <is>
-          <t>Δp difference 1.8%</t>
-        </is>
-      </c>
-      <c r="I7" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="H7" s="33" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="24" t="n"/>
@@ -2705,16 +2632,16 @@
         <v>2</v>
       </c>
       <c r="D5" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Evidence that the simulation software has been tested, version-controlled, and is fit for turbomachinery RANS simulations.</t>
+          <t>Solver is a recognized commercial code with documented version control; regression and benchmark testing present.</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024R1 is a commercially certified solver. Solver version and UDF checksums are logged. Case files and scripts are under Git LFS with tags; run cards capture all solver settings. RHEL 8.8 OS documented. Toolchain sanity-checked against canonical benchmarks (laminar pipe, backward-facing step, rotating cavity) within published tolerances. Cross-code check with OpenFOAM v10 at one point (1.8% difference) provides additional code-level confidence. No formal ISO 9001 quality process citation, but reproducibility procedures are documented.</t>
+          <t>ANSYS Fluent 2024R1, double precision; solver version and UDF checksums logged. Toolchain verified on three canonical benchmark cases (laminar pipe, backward-facing step, rotating cavity) with results within published tolerances. Cross-code comparison with OpenFOAM v10 at one operating point (1.8% Δp difference). Mesh, case files, and scripts under Git LFS with tags; any figure reproducible from repository in &lt;2 hours. OS and hardware documented (RHEL 8.8, dual EPYC 7543).</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2742,12 +2669,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Evidence that Fluent correctly solves the governing RANS equations for this class of problem.</t>
+          <t>Code correctly solves governing equations as demonstrated by benchmark comparisons.</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Canonical benchmark cases (laminar pipe flow, backward-facing step, rotating cavity) were run and results matched published references within published tolerances. Cross-solver comparison with OpenFOAM v10 at one fan operating point shows 1.8% Δp agreement. These together provide adequate numerical code verification for steady RANS in rotating machinery at this assurance level.</t>
+          <t>Benchmark problems (laminar pipe, backward-facing step, rotating cavity) run with results matching published references. Cross-code OpenFOAM v10 check at one operating point yields 1.8% Δp difference. No formal Method of Manufactured Solutions documented, but benchmark suite and cross-code agreement provide adequate evidence for MRL 2 context.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2775,12 +2702,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Grid-induced uncertainty quantified and shown to be small relative to acceptance thresholds.</t>
+          <t>Mesh convergence demonstrated quantitatively; grid-induced uncertainty reported.</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three grids (6.1M, 12.4M, 24.8M cells) run with the same setup; y+ ≈ 1 on the fine grid. Monotonic convergence confirmed. Richardson extrapolation applied; grid-induced uncertainty is 1.1% on Δp and 1.9% on power, both well below the 5%/7% acceptance thresholds. This is a thorough, quantified mesh convergence study.</t>
+          <t>Three grids (6.1M, 12.4M, 24.8M cells) with monotonic convergence confirmed. Richardson extrapolation performed; grid-induced uncertainty quantified as 1.1% on Δp and 1.9% on power. Fine-grid y+ ≈ 1 on walls. Iterative remainder estimated at &lt;0.2% from restart tests. Results incorporated into combined uncertainty budget.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2808,12 +2735,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Iterative convergence demonstrated to be negligible relative to acceptance thresholds.</t>
+          <t>Solver residuals and monitor quantities demonstrate adequate convergence.</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Residuals reduced 3–4 orders of magnitude. Mass and torque monitors leveled to within 0.1% over the last 800 iterations. Iterative remainder estimated at &lt;0.2% from restart tests. This is well-quantified iterative solver convergence documentation.</t>
+          <t>Residuals reduced 3–4 orders of magnitude. Mass and torque monitors leveled to within 0.1% over the last 800 iterations. Pseudo-transient ramp with pressure–velocity coupled scheme used. Iterative remainder estimated at &lt;0.2% from restart tests. Double precision arithmetic throughout.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2841,12 +2768,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Evidence that the model was set up correctly with appropriate boundary conditions, mesh quality, and independent review.</t>
+          <t>Independent review of model setup; boundary conditions and mesh quality verified.</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Boundary conditions are physically motivated and documented: inlet uses total pressure and measured 3% turbulence intensity, outlet fixed static pressure, wall roughness 12 μm from profilometer (not tuned). Upstream/downstream ducts at 4D/6D minimize end effects. Tip clearance from CMM. Internal reviewer A. Carver (independent of the project) ran a checklist and spot-checked two meshes. Analysts completed Fluent advanced turbomachinery training; onboarding playbook governs boundary setup and y+ targeting. Repository rebuild demonstrated in &lt;2 hours.</t>
+          <t>Internal independent reviewer (A. Carver, not on project) ran the setup checklist and spot-checked two meshes. Lab team collected validation data blind to mid-course CFD results. Boundary conditions documented: inlet total pressure with 3% TI, fixed static pressure outlet, wall roughness 12 μm from profilometer (not tuned). Duct lengths 4D upstream / 6D downstream. Analysts completed Fluent advanced turbomachinery training; new-hire onboarding playbook for BCs and y+ targeting. Run card captures all solver settings.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2874,12 +2801,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Mathematical model selection justified for the physics regime; known limitations documented.</t>
+          <t>Governing equations and turbulence model selection justified; known limitations documented.</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Steady RANS with k-ω SST and curvature correction is appropriate for Re ~3e5 in-duct axial fan at design-range operating points. MRF approach for rotor treatment is standard for this class. Incompressible, isothermal treatment justified at these conditions. Model-form spread quantified via SST vs SA comparison (≤2.5% Δp). Known limitations explicitly stated: no stall modeling, no acoustics, no transient blade-passage resolution. Scope limits documented (0.10–0.26 kg/s, 2300–3800 rpm).</t>
+          <t>Steady RANS with k-ω SST and curvature correction selected for Re ~3×10^5 rotating flow; MRF rotor treatment applied. Incompressible isothermal assumption justified for ambient air. Model-form uncertainty quantified by comparison with Spalart–Allmaras (≤2.5% Δp bias), contributing 2.0% to combined uncertainty. Known limitations explicitly documented: no stall modeling, no acoustics/tonal content, no transient blade-passage resolution. Out-of-scope conditions stated.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2907,12 +2834,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Input data traceable to measurements; key input sensitivities characterized.</t>
+          <t>Key model inputs traceable to measurements; input uncertainty characterized.</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>All major inputs trace to physical measurements: tip clearance from CMM (0.38 mm), RPM from controller readback verified against optical tach to ±0.1%, wall roughness 12 μm from profilometer, ambient density from lab barometer/thermometer, turbulence intensity 3% (sensitivity tested 1–5%, &lt;0.8% Δp shift). One-at-a-time sensitivity sweeps performed for RPM, tip clearance, and inlet turbulence. Input uncertainty contribution to combined UQ is 2.1% (dominated by tip gap). Fillets &lt;0.2 mm suppressed and documented.</t>
+          <t>RPM verified from controller readback vs. optical tach to within 0.1%. Tip clearance from CMM (0.38 mm). Wall roughness from profilometer data (12 μm). Ambient density from lab barometer/thermometer. Inlet TI sensitivity swept 1–5% (Δp shift &lt;0.8%). One-at-a-time sensitivity: RPM dominant (∂Δp/∂RPM ≈ 1.7 Pa/rpm), tip gap +0.2 mm → −2.1% Δp. Input uncertainty contribution 2.1% (tip gap dominant), incorporated into combined RSS uncertainty budget.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2940,12 +2867,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Test articles are production-representative; adequate number of test points.</t>
+          <t>Adequate number of test conditions; test articles representative of production geometry.</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Testing performed on the production fan (same geometry as CAD, same tip clearance) on the E-14 rig at Gantt Lab. Nine operating points tested per ISO 5801, covering the stated operating envelope. One hold-out point (3200 rpm, 0.18 kg/s) reserved and not seen during model setup. No formal statistical characterization of multiple specimens (single unit tested), which is typical for this class of internal aerodynamics validation. Lab team collected data blind to CFD mid-course results.</t>
+          <t>Nine operating points measured across the envelope (0.12–0.24 kg/s, 2400–3600 rpm), including one blind hold-out (3200 rpm / 0.18 kg/s). Testing performed on the E-14 rig at Gantt Lab per ISO 5801. Geometry is from production CAD. Number of replicate specimens not explicitly stated, but nine operating points provide reasonable coverage. No formal statistical sample-size justification documented.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2973,12 +2900,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Test conditions well-controlled and measured with quantified uncertainty; calibrated instrumentation.</t>
+          <t>Calibrated instrumentation; measurement uncertainty quantified; standard test protocol followed.</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Testing conducted per ISO 5801 standard. Instrumentation: static taps ±0.25% FS, calibrated orifice plate for mass flow, optical tachometer ±0.2% RPM, lab barometer/thermometer for ambient density. Data uncertainty quantified: 1.5% for Δp, 1.2% for power across the envelope. Ambient air at 25°C documented. Controlled laboratory environment. Calibration traceability implied by ISO 5801 compliance.</t>
+          <t>Testing per ISO 5801. Static taps at ±0.25% FS; mass flow via calibrated orifice plate; RPM via optical tach (±0.2%). Data uncertainty: 1.5% on Δp, 1.2% on power across the envelope. Lab team collected data blind to CFD mid-course results, reducing bias risk. Ambient conditions (density) measured with barometer/thermometer.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3006,12 +2933,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model inputs demonstrably match experimental test conditions; input uncertainty propagated.</t>
+          <t>CFD input parameters demonstrably match experimental test conditions.</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Comprehensive input-to-measurement traceability: RPM from same controller readback matched to tach, tip gap from CMM used directly in CAD/mesh, roughness from profilometer applied as model input, ambient conditions from rig instrumentation. Input uncertainty contributions explicitly propagated (2.1% on Δp from tip gap dominating). One-at-a-time sensitivity analysis confirms which inputs matter most. No post hoc tuning of model inputs to match test data beyond measured roughness.</t>
+          <t>RPM in CFD taken from controller readback verified against optical tach (±0.1%). Tip clearance matched to CMM measurement. Wall roughness set to profilometer value. Ambient density matched from lab measurement. Inlet TI set to 3% consistent with rig inlet conditions. Input-to-experiment correspondence explicitly verified for all dominant sensitivity parameters. Input uncertainty contributions propagated and reported.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3039,12 +2966,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to experimental data with combined uncertainty; comparison covers the operating envelope.</t>
+          <t>Quantitative metrics for QoI comparison; uncertainty bands included; no post-hoc tuning.</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Predictions compared to ISO 5801 data across nine operating points for both Δp and power. Metrics: RMS error 3.2% Δp (threshold 5%), RMS error 4.6% power (threshold 7%), worst-case 5.6% power near low-flow end. Hold-out point at 3200 rpm/0.18 kg/s tested blind. Combined uncertainty budget (grid 1.3%, model-form 2.0%, inputs 2.1%, RSS ~3.2% Δp) underpins the acceptance argument. Comparison uses percent error on QoIs plus error-normalized score combining model and test uncertainty. No rescaling or offsetting. Physical explanation offered for worst-case miss (inlet swirl at low flow).</t>
+          <t>Percent error on Δp and power computed across nine operating points. RMS error 3.2% Δp, 4.6% power; worst-case 5.6% power at low-flow end. Hold-out point (3200 rpm / 0.18 kg/s) reserved and compared blind. Error-normalized score combining model and test uncertainty used as comparison metric. No re-scaling or post-hoc parameter tuning applied. Combined model uncertainty ~3.2% on Δp (RSS of grid 1.3%, model-form 2.0%, inputs 2.1%). Both QoIs within pre-specified acceptance thresholds (5% Δp, 7% power).</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3072,12 +2999,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>Model outputs directly address the decision (fan selection, operating point); QoIs measurable both computationally and experimentally.</t>
+          <t>QoIs directly address the design decision; measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>QoIs are fan pressure rise (Δp) and shaft power (torque), which are exactly the quantities needed for fan selection and thermal margin assessment. Both are directly predicted by the CFD model and directly measured by the ISO 5801 test rig. Success criteria (5% Δp, 7% power) were set up front with the thermal team and are physically motivated by the design decision consequences. No mismatch between computational and experimental output definitions.</t>
+          <t>Δp (pressure rise) and torque/power are the direct quantities driving fan selection and thermal margin decisions, as agreed with the thermal team. Both are measurable in CFD (from pressure and torque monitors) and in the test rig (static taps, orifice plate, tach). Success criteria (5% Δp, 7% power) established up-front with the thermal team before analysis. QoIs are precisely the quantities on which the go/no-go decision is based.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3105,12 +3032,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions match the intended operating envelope; gaps explicitly documented.</t>
+          <t>Validation conditions match intended operating envelope; gaps documented.</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation covers the stated operating envelope (0.12–0.24 kg/s, 2400–3600 rpm) with nine points and a blind hold-out. Same geometry, same fluid (ambient air, 25°C), same turbulence closure. Scope limits explicitly documented: model not valid beyond 0.10–0.26 kg/s or 2300–3800 rpm; stall and near-stall operation not covered; acoustic predictions not in scope; transient blade-passage effects not resolved. Minor gap: single test unit rather than production-lot statistical sample. Physical explanation provided for observed deviation at low-flow boundary (inlet swirl). Coverage is good but near-boundary applicability has acknowledged limitations.</t>
+          <t>Validation covers 0.12–0.24 kg/s and approximately 2400–3600 rpm, matching the stated COU envelope. Same geometry (production CAD), same fluid (ambient air, 25°C), same measurement approach (ISO 5801) used in validation and intended application. Minor gap: low-flow end shows larger discrepancy (5.6% power) attributed to inlet swirl; noted as scope limit. Explicit out-of-scope statements: stall, acoustics, cavitation, operation outside 0.10–0.26 kg/s / 2300–3800 rpm. MRF (not transient) treatment is adequate for steady operating points but not for near-stall or tonal analysis — gap explicitly acknowledged.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3199,7 +3126,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The steady RANS MRF model meets all pre-established acceptance criteria: RMS error of 3.2% on Δp (threshold 5%) and 4.6% on shaft power (threshold 7%) across nine ISO 5801 operating points including a blind hold-out. A combined uncertainty budget of ~3.2% on Δp (RSS of grid, model-form, and input contributions) is well-characterized and consistent with the observed validation errors. Mesh convergence, iterative convergence, input traceability, independent review, and explicit scope limitations are all documented. The model is accepted for fan selection and operating point decisions within the stated envelope (0.12–0.24 kg/s, 2400–3600 rpm, ambient air at 25°C). Use outside this envelope, near stall, or for acoustic predictions requires transient URANS/LES and new validation data as explicitly noted.</t>
+          <t>The model meets all pre-specified success criteria: RMS errors of 3.2% (Δp) and 4.6% (power) are within the agreed 5% and 7% thresholds respectively, with worst-case power error of 5.6% at the low-flow extremity still within threshold and attributed to documented rig asymmetry. Combined uncertainty budget (RSS ~3.2% on Δp) is quantified and tractable. Mesh convergence, solver convergence, input traceability, independent setup review, blind hold-out validation, and ISO 5801 test protocol all demonstrate adequate rigor for a design-guidance-grade, MRL 2 decision. Scope limitations (stall, acoustics, near-stall transient) are explicitly documented. Model is accepted for fan selection and operating-point decisions within 0.12–0.24 kg/s and 2400–3600 rpm; use outside this envelope or for acoustic/stall assessment requires additional validation activities.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3209,14 +3136,10 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>P. Nguyen</t>
-        </is>
-      </c>
-      <c r="E3" s="39" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
+          <t>P. Nguyen, V&amp;V Coordinator</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="24" t="n"/>
